--- a/mode_docx_gen/pmi_lodzt/lot_modes/ЛО Т_5.xlsx
+++ b/mode_docx_gen/pmi_lodzt/lot_modes/ЛО Т_5.xlsx
@@ -1695,9 +1695,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
